--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>45853</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>46051</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45026</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>46170</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45776</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>46182</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>45503</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45776</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44468</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>44999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>44827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>44627</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>45897</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>45931</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45931</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>44847</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45629</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>45734</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>45237</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>46185</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46200</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>45261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45841</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>46162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>45974</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>45974</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>46234</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>46279</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>46241</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45257</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>44525</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44797</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>44532</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>44479</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
         <v>44488</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>44484</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>44532</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44472</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44683</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44770</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44468</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>44721</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>44673</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>44553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>44967</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>45488</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45463</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>45313</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>45523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>45191</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45579</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44914</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44914</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>44623</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>45322</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>45456</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7780,7 +7780,7 @@
         <v>44810</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45386</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45558</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>44512</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45583</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45762</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45138</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44530</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>44945</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>44888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>44623</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         <v>44915</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44701</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8739,7 +8739,7 @@
         <v>44741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44655</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         <v>45477</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>44606</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>45159</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44840</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9187,7 +9187,7 @@
         <v>45356</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44516</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>45166</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44722</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9479,7 +9479,7 @@
         <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45734</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>45035</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45749</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45560</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>45099</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45278</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45671</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>45035</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>45235</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>45896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45219</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>45734</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>45770</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>45076</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>45401</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45477</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45910</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45537</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45915</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>44516</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>44839</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44757</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>45190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45931</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45931</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45523</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45737</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45603</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>45672</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12308,7 +12308,7 @@
         <v>45959</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45189</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44757</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44628</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>44837</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>46154</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45448</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44847</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45968</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>46155</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>45974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45176</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>46154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>44530</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13350,7 +13350,7 @@
         <v>45978</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44936</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>45979</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13569,7 +13569,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>45982</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44757</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>45077</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>45077</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>46157</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>46157</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45992</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>45448</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>45404</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>46163</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14543,7 +14543,7 @@
         <v>46163</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45775</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45551</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45273</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44988</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45999</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44671</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>44896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>44467</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>44897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>46007</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>46013</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>46169</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45034</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46007</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45764</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45764</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44810</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44810</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>44755</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45159</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44476</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>46170</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>46170</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>45219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45219</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45152</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>46044</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45463</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>46178</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>44751</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45547</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46178</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>46178</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17279,7 +17279,7 @@
         <v>46178</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>46178</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45659</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>46182</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44545</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>46182</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45618</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>45579</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>44574</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18029,7 +18029,7 @@
         <v>45510</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>45189</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>46185</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>46185</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>45219</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18404,7 +18404,7 @@
         <v>46094</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>46196</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>46196</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>46104</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>45170</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>46104</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>45553</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18940,7 +18940,7 @@
         <v>45392</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44911</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45021</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45392</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45370</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45370</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45051</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>44985</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45160</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44810</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45098</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19743,7 +19743,7 @@
         <v>45358</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45680</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45480</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45264</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44908</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45076</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44581</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44839</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20405,7 +20405,7 @@
         <v>45078</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>45418</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>44733</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20624,7 +20624,7 @@
         <v>45273</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44757</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>44529</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46260</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45227</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46260</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45762</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44678</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>46266</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21369,7 +21369,7 @@
         <v>46266</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21447,7 +21447,7 @@
         <v>44658</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>44658</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45734</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>44508</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45779</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>45603</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21895,7 +21895,7 @@
         <v>45783</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45667</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>45974</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>45937</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>45630</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>46051</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46234</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45601</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>46051</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46234</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45303</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22806,7 +22806,7 @@
         <v>45665</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>45525</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>46241</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45480</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>46241</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45665</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>46241</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23566,7 +23566,7 @@
         <v>45480</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45798</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45798</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>45669</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23868,7 +23868,7 @@
         <v>45798</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45798</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45798</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45803</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45810</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45812</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45691</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>45820</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45826</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45832</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45832</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>45834</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45834</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45834</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45779</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>44470</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45826</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45873</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44712</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45834</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45734</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45734</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45734</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>45931</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46170</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44917</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45026</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45776</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45503</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45776</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44468</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45734</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45897</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45931</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45931</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>44847</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44999</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46200</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45974</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46234</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45261</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46241</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46162</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45257</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>44525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44797</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44472</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>44683</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>44797</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44658</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44839</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45227</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45386</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45322</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44757</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44810</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45463</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45138</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>46007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45273</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45480</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45665</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45798</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45480</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45798</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45798</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45798</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45798</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44945</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45669</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45749</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45671</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45551</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45558</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45803</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44914</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45737</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45152</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45931</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44936</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45810</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45404</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46094</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44476</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46104</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>46104</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44655</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45618</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45968</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45583</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45974</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45356</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45978</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45979</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45982</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45159</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45659</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45770</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45477</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45999</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45999</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45537</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>46007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45051</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46013</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44733</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45764</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45764</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45273</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45672</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45264</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44530</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45887</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45826</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45235</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44897</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45832</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45832</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>46154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45834</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>46154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45834</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45834</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>46157</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45547</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45992</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>46157</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46160</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44508</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>46163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44545</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45779</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45358</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44470</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>46169</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45418</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>46170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45488</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44530</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45278</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45078</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>46178</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>46178</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45477</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46178</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>46178</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46178</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>46178</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>46182</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>46182</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46185</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44516</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45160</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44512</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45775</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45370</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45191</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44628</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45170</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46196</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44606</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45762</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44658</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44658</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>46260</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45456</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>44757</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45190</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45219</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45680</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44757</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45076</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45974</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45264</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>46234</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45392</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46234</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46241</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>46241</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>44678</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44908</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45034</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44911</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45021</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45189</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45463</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45313</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>44967</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45035</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44516</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44914</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44553</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45189</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44837</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44529</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45551</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45176</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45523</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44839</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44701</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44755</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45219</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45392</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45579</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45579</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44810</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45510</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45219</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45448</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45734</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45779</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45630</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45603</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45783</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45667</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45601</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45665</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45525</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>44712</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45734</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45734</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45931</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46170</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>44917</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>45026</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45776</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45503</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45776</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44468</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45734</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45897</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45931</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45931</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>45841</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>44847</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>46163</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44999</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>46185</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>46200</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>45629</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44827</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>45974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45974</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>46234</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45261</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>46241</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>46162</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>44627</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>45257</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>44525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44797</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44472</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>44683</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>44613</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>44797</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>44868</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
         <v>44553</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>44658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>44658</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44770</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44545</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>44496</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>44468</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>44721</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44673</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45035</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>44839</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45227</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45386</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45322</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>44810</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>44757</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44810</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44834</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>44847</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45463</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45138</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>46007</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44840</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45273</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45480</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45665</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45798</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45480</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45798</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45798</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45798</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>45798</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45798</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44945</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>45669</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45749</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45480</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45671</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45896</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46044</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>45551</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44671</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9609,7 +9609,7 @@
         <v>45910</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>45910</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45910</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         <v>45558</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45803</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44914</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45915</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>45737</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44623</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>45560</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44896</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45152</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45931</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>44936</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45810</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45404</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>46094</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44476</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46104</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>46104</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44655</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45959</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45762</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45098</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45618</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45812</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45968</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45583</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45974</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45691</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45356</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45978</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45979</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45982</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45159</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45401</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45659</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>45770</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45477</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45999</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45999</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45537</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>44581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44757</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>46007</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45051</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46013</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44733</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45764</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45764</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45273</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         <v>45672</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>45264</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14001,7 +14001,7 @@
         <v>44530</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>45887</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>44985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>44915</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45826</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>46141</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14517,7 +14517,7 @@
         <v>45235</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44897</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45832</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14741,7 +14741,7 @@
         <v>45832</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>46154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45834</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>46154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45834</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>45834</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>46155</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>46157</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45547</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45992</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>46157</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>46160</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45553</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44508</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45077</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45077</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>46163</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>46163</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>46163</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44545</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45779</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45358</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16397,7 +16397,7 @@
         <v>44470</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16470,7 +16470,7 @@
         <v>46169</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45418</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45826</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16689,7 +16689,7 @@
         <v>46170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45488</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>44530</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>45278</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45078</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45166</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>46178</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>46178</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45477</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>46178</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>46178</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17580,7 +17580,7 @@
         <v>46178</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17653,7 +17653,7 @@
         <v>45099</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>46178</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>46182</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17877,7 +17877,7 @@
         <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>46182</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>46185</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46185</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>44516</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>45160</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>44512</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>45873</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45775</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45370</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18700,7 +18700,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45191</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>44628</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45170</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>46196</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19075,7 +19075,7 @@
         <v>46196</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>44606</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44810</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45974</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45762</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>44658</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44658</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>46260</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45456</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>46260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>44757</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>45190</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>45219</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45680</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44757</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45076</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45974</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45264</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20955,7 +20955,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21033,7 +21033,7 @@
         <v>46234</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>46051</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45392</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46234</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45448</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46241</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>46241</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21647,7 +21647,7 @@
         <v>44678</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44908</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44574</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45034</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>44911</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>45021</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>45189</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45463</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45313</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>44967</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>44623</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45035</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44516</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44914</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>44553</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>45189</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44741</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44837</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>44529</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45551</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45176</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45159</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45734</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>44967</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45523</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44839</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>44751</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23638,7 +23638,7 @@
         <v>45603</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>44701</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>44755</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>45219</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45392</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45579</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45579</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>44810</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45510</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45219</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45448</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>45734</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24524,7 +24524,7 @@
         <v>45779</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45630</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45603</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>45783</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45667</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>45601</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45303</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45665</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45525</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25186,7 +25186,7 @@
         <v>44712</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45834</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45734</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>45734</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45931</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>46196</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45026</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>46170</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45776</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45503</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45776</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>44999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45897</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45931</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45931</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45841</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44847</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45237</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46200</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>46279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46241</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>46290</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45974</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45257</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44532</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44479</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44825</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44831</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44532</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44472</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44683</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44868</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44658</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44538</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44770</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45488</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44967</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45191</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44914</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44914</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45579</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45456</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>45303</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45749</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45665</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>46007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>46013</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44512</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>46007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45138</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44530</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>45910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>45910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44945</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>45798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45480</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45798</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45669</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45798</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45798</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45803</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45159</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45931</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44623</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44915</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44741</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44655</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45810</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44606</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45959</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45691</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>46094</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45356</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45968</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45166</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45979</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45982</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45035</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45560</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45832</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45278</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45834</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45834</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45219</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45076</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45477</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44834</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45779</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44516</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44839</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44757</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45734</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45770</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45401</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45887</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45523</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>46141</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45737</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45873</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45603</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45672</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45189</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44757</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>46155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44628</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46154</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44837</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45448</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>46157</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44847</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46157</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45176</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>46163</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>46163</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44936</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45264</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44757</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46169</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45077</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>46170</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46178</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45448</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46178</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46178</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46178</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46178</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46178</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45775</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45551</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>46182</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46182</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>46185</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44896</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46196</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45764</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44810</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45159</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44476</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45219</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45219</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45152</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45974</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46260</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46260</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44751</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45547</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>46266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45659</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44545</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45579</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45510</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45189</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46051</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46234</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46234</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45219</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45553</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45392</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>44911</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>46241</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46241</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45392</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45370</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45370</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45160</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44810</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45098</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45358</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45680</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45480</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46297</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45264</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>44908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45076</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44581</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44839</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45418</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45273</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44757</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44529</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45227</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45762</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44678</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44658</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44658</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44508</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45779</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45603</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45783</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45667</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45630</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44712</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45834</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45734</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45734</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45931</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>44917</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45026</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>46170</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>45776</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45503</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45776</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>44530</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>44999</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45897</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45931</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>45931</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45841</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44847</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>45629</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>45237</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46200</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45734</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>46206</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45974</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>46234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>46279</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46241</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>46290</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>45974</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45257</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44525</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>44797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>44532</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>44479</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>44484</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>44614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>44825</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44831</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44532</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44472</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44683</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44868</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44658</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44538</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44770</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>45488</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>45313</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44967</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45191</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44914</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44914</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>45579</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>45456</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>45303</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>45749</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>45665</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>46007</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45525</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>46013</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45386</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44512</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>46007</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45558</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>45671</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>45762</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>45896</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>45583</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45138</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44530</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45910</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>45910</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>45910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>44945</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>45798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>45480</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>45798</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>45669</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>45798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>45798</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45798</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45803</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45159</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45931</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44623</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44915</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44701</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>44741</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44655</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45477</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>45810</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44606</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44840</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11017,7 +11017,7 @@
         <v>45812</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>45959</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>45691</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>46094</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>45356</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>45968</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>45166</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>45974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11684,7 +11684,7 @@
         <v>46104</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11762,7 +11762,7 @@
         <v>44722</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45219</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11908,7 +11908,7 @@
         <v>46104</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11986,7 +11986,7 @@
         <v>45978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>45979</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         <v>45982</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45820</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>45035</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45560</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45826</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45832</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45832</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45278</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45834</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45834</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45834</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>45170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         <v>45235</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         <v>45219</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45076</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>45477</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>44834</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>45779</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>44516</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>44839</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45264</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44757</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45734</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45770</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45401</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45190</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45887</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45826</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45523</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>46141</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45537</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>44967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>45737</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45873</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>45603</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45672</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15268,7 +15268,7 @@
         <v>45189</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15341,7 +15341,7 @@
         <v>44757</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>46155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>44628</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46154</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>44837</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45448</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>46157</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44847</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46157</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46160</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45992</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>45176</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>46163</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>46163</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>46163</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>44530</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>44936</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45264</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44757</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46169</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>45077</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>46170</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>46170</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>46178</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45448</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45404</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>46178</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>46178</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46178</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46178</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>46178</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45775</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45551</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>46182</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>44988</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46182</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46182</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44671</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>46185</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44896</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>46196</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>46196</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45764</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>44810</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>44755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45159</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44476</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45219</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45219</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45152</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45974</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46260</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45463</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46260</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>44751</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45547</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>46266</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20206,7 +20206,7 @@
         <v>45659</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>44545</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45618</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45579</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44574</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45510</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45189</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46051</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46234</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46234</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45219</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>45170</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45553</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45392</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>44911</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46241</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45021</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21555,7 +21555,7 @@
         <v>46241</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46241</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45392</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45370</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45370</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45051</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>45974</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45160</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>44810</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45098</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45358</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45680</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45480</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46297</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45264</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22743,7 +22743,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>44908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>45076</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>44581</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44839</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>45078</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45418</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>44733</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45273</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>44757</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23478,7 +23478,7 @@
         <v>44529</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23551,7 +23551,7 @@
         <v>45227</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>45551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45762</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>44678</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44658</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>44658</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45734</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>44508</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45779</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45603</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45783</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45667</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45630</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45601</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>44712</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45834</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45734</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45734</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45734</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45931</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46196</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45776</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44917</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>45026</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45503</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44530</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44627</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>44827</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>46200</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>46234</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45974</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>46303</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45257</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44797</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44658</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44683</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44658</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44721</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44553</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44810</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45159</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45035</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45734</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44967</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44751</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44839</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>44834</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44757</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45553</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>44810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44701</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>45322</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45077</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45358</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45463</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>45138</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45579</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>44810</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45418</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45273</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45749</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44530</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45278</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45219</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45671</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45896</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45448</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45734</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45480</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45166</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45477</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45099</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45779</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45630</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45603</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45915</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45783</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45558</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44914</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45667</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45737</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45219</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45601</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44516</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45160</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>44512</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45370</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45370</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44623</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45560</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44896</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45191</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44628</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45303</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45665</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45525</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45152</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45931</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45480</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45665</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45798</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45798</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45798</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45404</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45669</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44606</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44722</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44810</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44655</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45762</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45812</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44658</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44658</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45762</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45098</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45618</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45826</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45456</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45583</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45832</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45832</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45356</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45834</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44757</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45159</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45968</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45974</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45190</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45779</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45659</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45477</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45826</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45680</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44757</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45076</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44581</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>44757</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45979</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45873</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45264</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44733</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45764</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45982</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44530</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44985</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45392</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>46104</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45448</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45235</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44678</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44908</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45999</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44911</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45021</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45463</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>46007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45313</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45401</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>46007</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45770</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44967</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45537</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44623</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45734</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45035</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44914</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44553</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44741</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44837</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45887</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44529</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46141</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46154</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>46155</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46157</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46157</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>46163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46163</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>46169</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>46170</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46170</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46178</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46178</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46178</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46178</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>46182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>46185</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46185</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46196</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45974</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>46266</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46266</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>46234</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>46234</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>46241</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46241</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46241</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45974</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45798</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>46297</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46302</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46302</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>46303</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>46303</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>46303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>46260</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46303</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46260</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>46182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44712</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45834</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45734</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46169</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45624</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>46051</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>45853</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45251</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45776</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>44917</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>45026</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>45503</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44530</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>44847</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>45734</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44627</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44999</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45897</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45629</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>44827</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45261</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45841</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>46200</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>46206</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>46234</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>46279</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>46241</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>46290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>45974</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
         <v>45974</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>46303</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45257</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>44525</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>44797</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44479</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44488</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44484</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44658</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44683</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>44658</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>44545</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44797</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>44721</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>44868</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>44770</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>44553</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         <v>44810</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>45176</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>44897</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>45159</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>44673</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>45219</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>45035</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         <v>45734</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44967</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>45523</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44839</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44751</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>45547</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44839</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45227</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>44834</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>44757</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45553</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>44810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>44701</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>45322</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45077</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45077</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>44755</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>45386</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44847</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8832,7 +8832,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45358</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>45392</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9051,7 +9051,7 @@
         <v>45463</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>45138</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>44840</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>45579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45579</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>44810</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>45510</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>45418</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45273</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>45488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>45749</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44530</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45278</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45219</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44945</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45671</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>45896</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45448</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>45734</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10521,7 +10521,7 @@
         <v>45480</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45166</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>45477</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         <v>45910</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45099</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>45779</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45630</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45603</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45915</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45783</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>45558</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44914</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11709,7 +11709,7 @@
         <v>44988</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45667</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11855,7 +11855,7 @@
         <v>45737</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45219</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>45601</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>44516</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45160</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12225,7 +12225,7 @@
         <v>44512</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>45370</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>45370</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44623</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>45560</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         <v>44896</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>45191</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12809,7 +12809,7 @@
         <v>44628</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>45170</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45303</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45665</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45525</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13179,7 +13179,7 @@
         <v>45152</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>45931</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13398,7 +13398,7 @@
         <v>45480</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13471,7 +13471,7 @@
         <v>45665</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>45480</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
         <v>45798</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>45798</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45798</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13851,7 +13851,7 @@
         <v>45798</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13929,7 +13929,7 @@
         <v>45798</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>45404</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45669</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>44888</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45803</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44606</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44722</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45076</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>44810</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44655</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>45762</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45812</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45691</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>44658</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>44658</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45762</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>45098</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45618</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45826</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45456</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45583</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>45832</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45832</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45959</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45356</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45834</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45834</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44757</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>45159</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45968</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45974</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>45190</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45779</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16695,7 +16695,7 @@
         <v>45659</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16768,7 +16768,7 @@
         <v>45219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16841,7 +16841,7 @@
         <v>45477</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45826</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45680</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>44757</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45076</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>44581</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>44757</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45979</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>45873</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45264</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>44733</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45764</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45273</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45264</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>45982</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>44530</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44985</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45392</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46104</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>46104</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44915</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>45448</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18764,7 +18764,7 @@
         <v>45235</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18837,7 +18837,7 @@
         <v>44678</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>44908</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44574</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>45999</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19202,7 +19202,7 @@
         <v>45999</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19275,7 +19275,7 @@
         <v>44911</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19348,7 +19348,7 @@
         <v>45021</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45189</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45463</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>46007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19640,7 +19640,7 @@
         <v>45313</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19713,7 +19713,7 @@
         <v>45401</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>46007</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45770</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44967</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45537</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>44623</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45734</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45035</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>44516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20385,7 +20385,7 @@
         <v>44914</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>44553</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>45189</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>44741</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>46044</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>45264</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>44837</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>45887</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>44529</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>45551</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46141</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>46154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46154</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>46155</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>46157</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>45992</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46157</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>46160</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>46094</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21802,7 +21802,7 @@
         <v>46163</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>46163</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21958,7 +21958,7 @@
         <v>46163</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>46169</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>46170</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46170</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46178</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22338,7 +22338,7 @@
         <v>46178</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22411,7 +22411,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>46178</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22630,7 +22630,7 @@
         <v>46178</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22703,7 +22703,7 @@
         <v>46182</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22781,7 +22781,7 @@
         <v>46185</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>46185</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46196</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23015,7 +23015,7 @@
         <v>46196</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23093,7 +23093,7 @@
         <v>45974</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>46266</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>46266</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>46234</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>46234</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>46241</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46241</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>46241</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45974</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23795,7 +23795,7 @@
         <v>46051</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45798</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>46297</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24029,7 +24029,7 @@
         <v>46051</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>46302</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46302</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>46303</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>46303</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>46303</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>46260</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46303</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46260</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46303</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>46182</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>44712</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45834</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45734</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25320,7 +25320,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46310</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46169</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45853</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45624</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44917</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45026</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>46170</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45776</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>44530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44999</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>45931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>46163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45629</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>46200</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45841</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>46234</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45257</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44488</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44683</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44770</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44721</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44967</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45488</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>45463</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45313</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45191</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45579</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44914</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44914</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45456</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45386</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44512</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45583</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45138</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44945</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45159</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44888</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44623</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44655</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45477</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>44701</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44516</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45166</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44722</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45219</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44741</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45734</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45560</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45734</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>45770</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45401</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45278</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45035</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45235</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45219</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45915</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45477</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44757</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>46154</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>46154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45737</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45968</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>46163</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45974</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45978</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45672</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45979</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45189</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44757</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44628</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44837</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>46169</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45176</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44530</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45999</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45999</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44936</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45264</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46170</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46170</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45077</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45077</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46007</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45404</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>46007</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44988</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44671</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>46178</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>46178</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44896</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46044</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46182</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45034</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45764</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44810</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44755</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>46185</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45159</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>46185</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45152</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>46196</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>46196</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46104</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46104</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45463</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44751</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45547</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45659</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45618</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45579</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44574</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45189</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45219</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45553</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45392</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44911</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45021</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45392</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45370</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45051</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45160</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45098</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46234</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46234</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45358</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45480</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45264</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44908</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45076</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46241</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46241</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44839</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46241</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45078</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45418</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>44733</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45273</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44757</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44529</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45227</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45551</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45762</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44678</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>46297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44658</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44658</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45734</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45798</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44508</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>46051</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46051</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45779</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45603</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45630</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>46303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>46303</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46303</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>46303</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>46260</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45303</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>46302</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46303</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45665</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>46260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45480</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45665</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45480</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45669</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>46182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45803</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>46266</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46302</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45810</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45812</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>46311</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45691</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45820</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45826</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45832</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45832</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45834</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45779</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44712</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45834</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45734</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46310</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46169</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45853</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45624</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44917</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45026</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>46170</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46182</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>46297</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>46303</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45503</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>45776</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>44530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44999</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>44827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>44627</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>45897</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>45931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>46163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44847</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>45629</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45734</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>46200</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45841</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46206</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>46234</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>46279</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45261</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46241</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>46290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>45974</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         <v>45974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5039,7 +5039,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45257</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44488</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44825</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44831</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44532</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44539</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44683</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44613</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44797</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44868</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44658</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44770</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44545</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44496</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44721</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44673</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>44553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44967</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>45488</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>45463</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
         <v>45313</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45191</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>45579</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44914</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>44914</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         <v>44623</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>45322</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45456</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         <v>44810</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45386</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44512</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45558</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45762</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45583</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45138</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44945</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>45159</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         <v>44888</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44623</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>44915</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44655</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45477</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44606</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         <v>44840</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         <v>44701</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>45356</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44516</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>45166</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44722</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>45219</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44741</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45734</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>45035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45560</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45734</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45896</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>45770</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45401</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>46141</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45278</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45035</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45170</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45235</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45910</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45910</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>45219</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>45915</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45076</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>45477</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11388,7 +11388,7 @@
         <v>44834</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44516</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>44839</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11607,7 +11607,7 @@
         <v>44757</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>45931</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>45190</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>46154</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>46155</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>46154</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>46157</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45959</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>46157</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>46160</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12508,7 +12508,7 @@
         <v>44967</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45737</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45968</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>46163</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>46163</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45974</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>46163</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45978</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45672</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45979</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45189</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13414,7 +13414,7 @@
         <v>45980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>44757</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13565,7 +13565,7 @@
         <v>45982</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44628</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44837</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>46169</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45176</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44530</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45999</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>45999</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44936</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45264</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46170</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14519,7 +14519,7 @@
         <v>46170</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>44757</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45077</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>45077</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>46007</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45448</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45404</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>46007</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45775</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45551</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>45273</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>44988</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>44671</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>46178</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>46178</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>46178</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>46178</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>46178</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44896</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46044</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46182</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45034</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45764</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44810</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44810</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44755</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>46185</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45159</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16739,7 +16739,7 @@
         <v>46185</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45219</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45152</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>46196</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>46196</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46104</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46104</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>45463</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44751</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45547</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45659</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44545</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45618</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>45579</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44574</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45189</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45974</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45219</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45553</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45392</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>44911</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45021</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18604,7 +18604,7 @@
         <v>45392</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>45370</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45370</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45051</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>45160</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>44810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45098</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46234</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>46234</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45358</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45480</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>45264</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>44908</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>45076</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44581</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46241</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>46241</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>44839</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>46241</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45078</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45418</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45974</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         <v>44733</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45273</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44757</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44529</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45227</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45551</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45762</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44678</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>46297</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44658</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44658</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>45734</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45798</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44508</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>46051</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>46051</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21579,7 +21579,7 @@
         <v>45779</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45603</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45783</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45630</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45601</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>46303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>46303</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46303</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>46303</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>46260</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22392,7 +22392,7 @@
         <v>45303</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>46302</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22538,7 +22538,7 @@
         <v>46303</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45665</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
         <v>45525</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>46260</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22913,7 +22913,7 @@
         <v>45480</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>45665</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45480</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45798</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45669</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>46182</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45798</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45798</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45803</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46266</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23824,7 +23824,7 @@
         <v>46266</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>46302</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23975,7 +23975,7 @@
         <v>45810</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45812</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>46311</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45691</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45820</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45826</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45832</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45832</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45834</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45834</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45834</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45779</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>45826</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45873</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44712</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>45834</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45734</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>45931</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>46196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46310</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46169</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45853</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45624</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44917</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45026</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>46170</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46182</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45776</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>44530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45897</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44627</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46200</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46234</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>46241</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45974</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45974</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>46303</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>45629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45261</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45257</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44532</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44683</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44868</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44658</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44538</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44770</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>45749</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45021</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45035</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>45227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45189</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45896</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>45463</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45313</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44967</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45910</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44623</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45915</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>46163</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44914</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44741</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>46169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46170</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45931</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>46170</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44837</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44529</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45176</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45159</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44757</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44810</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>46178</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45734</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>46178</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46178</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>46178</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45523</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>46178</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44839</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44751</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>46182</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45959</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46185</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44847</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45968</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46196</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45392</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45579</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44810</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45510</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45979</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45448</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45138</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45779</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45630</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45783</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>46007</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>46234</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45667</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45601</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>46234</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>46007</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44840</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>46241</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45303</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45665</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>46241</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>46241</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45525</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45480</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45798</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45798</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45798</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45798</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45669</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45691</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45974</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45826</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45832</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45832</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45798</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46297</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45834</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>46104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>46104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45779</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46302</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45826</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45480</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>46303</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>46303</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>46303</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>46260</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46303</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46303</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45873</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45798</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46182</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44671</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44914</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45401</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46266</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45737</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45770</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45219</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>46302</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45734</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45560</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46315</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>46311</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45264</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45152</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>44936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45887</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45404</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44888</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46141</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>46154</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44655</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>46155</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46157</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46157</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>46160</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45762</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45618</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45159</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45659</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45477</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44581</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44757</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45051</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>44733</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45764</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45273</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45672</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>44530</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45235</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45547</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45553</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>44508</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45077</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>44545</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45358</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45418</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44530</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45278</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45078</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45166</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45477</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44516</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45160</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44512</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45775</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45370</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44606</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44810</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45762</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44658</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44658</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45456</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45170</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>44757</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45190</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45219</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45680</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44757</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45076</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45264</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45264</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45392</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45448</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44908</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44911</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>44712</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45834</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46196</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>

--- a/Översikt KÖPING.xlsx
+++ b/Översikt KÖPING.xlsx
@@ -601,7 +601,7 @@
         <v>45548</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>46310</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>46169</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>45853</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45624</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>46051</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>46310</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>45251</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>44917</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45026</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>46170</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45776</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>46182</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45503</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>46297</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>45776</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>46303</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>44530</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>45897</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>46163</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>45734</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>44627</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>46200</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>46206</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46234</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>46279</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>46241</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>46290</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45974</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>45974</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>46303</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>45841</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>44847</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>44999</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>45629</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>45261</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>45257</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>44525</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44797</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>44532</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44825</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>44831</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44532</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44683</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44797</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44868</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44658</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44658</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44538</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44770</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>44545</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         <v>44496</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
         <v>44721</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>44673</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>45749</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>45021</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>45035</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>44839</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>45227</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         <v>45671</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45189</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45896</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7376,7 +7376,7 @@
         <v>45463</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45322</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45313</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7595,7 +7595,7 @@
         <v>45386</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44810</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>44967</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45910</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>45910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7970,7 +7970,7 @@
         <v>45910</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         <v>44623</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>46163</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>46163</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45915</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>46163</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45035</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44516</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>44914</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>45189</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44741</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>46169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>46170</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>45219</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>45931</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>46170</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44837</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44529</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>45176</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>45159</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44757</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9762,7 +9762,7 @@
         <v>44810</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>46178</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>46178</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45734</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>44967</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>46178</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46178</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>46178</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>45523</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>46178</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44839</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>44751</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>46182</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10726,7 +10726,7 @@
         <v>45603</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44701</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>46185</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45959</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>46185</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44755</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44847</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>45968</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45974</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>46196</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>45392</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>46196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45978</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>45579</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>45579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>44810</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>45980</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45510</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>45979</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45982</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45448</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45463</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>45138</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12752,7 +12752,7 @@
         <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>45779</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>45630</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13049,7 +13049,7 @@
         <v>45603</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45783</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>46007</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>46234</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45667</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45601</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13492,7 +13492,7 @@
         <v>46234</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13570,7 +13570,7 @@
         <v>46007</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>44840</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>46241</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45303</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45665</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>46241</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>46241</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45525</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45480</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45665</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>46044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45480</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45798</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45798</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14617,7 +14617,7 @@
         <v>45798</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>45798</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45798</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45669</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>45803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45810</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45273</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45812</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45691</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45974</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15450,7 +15450,7 @@
         <v>45826</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15523,7 +15523,7 @@
         <v>45832</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45832</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>46051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45798</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45834</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>46297</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45834</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45834</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>46051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44945</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>46104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>46104</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45779</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>46302</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45826</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
         <v>45480</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>46303</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>46303</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>46303</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>46260</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46303</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46260</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>46303</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45873</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45798</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>46182</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>45551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17564,7 +17564,7 @@
         <v>44671</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
         <v>45558</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>44914</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45401</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>46266</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46266</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>45737</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         <v>45770</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>45219</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>46302</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45734</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>44623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45560</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44896</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>46315</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>46311</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45264</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45152</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>44936</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19049,7 +19049,7 @@
         <v>45887</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45404</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>46317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44888</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>46141</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44722</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46154</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>46154</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>44655</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>46155</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19799,7 +19799,7 @@
         <v>46157</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46157</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>46160</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20101,7 +20101,7 @@
         <v>45762</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>45098</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20247,7 +20247,7 @@
         <v>45618</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
         <v>45583</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>45356</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>45159</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45659</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>45477</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>44581</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44757</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>45051</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>44733</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>45764</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45273</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>45672</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>44530</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44985</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>44915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45235</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45547</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45553</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>44508</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45077</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45077</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>44545</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45358</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>45418</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45488</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>44530</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>45278</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45078</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22452,7 +22452,7 @@
         <v>45166</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22525,7 +22525,7 @@
         <v>45477</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45099</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44988</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>44516</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45160</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>44512</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45775</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45370</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>45370</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45191</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>44628</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23333,7 +23333,7 @@
         <v>45170</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44606</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45076</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>44810</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45762</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23703,7 +23703,7 @@
         <v>44658</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44658</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45456</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45170</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24005,7 +24005,7 @@
         <v>44757</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>45190</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45219</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45680</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44757</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45076</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>45264</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>45264</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>45392</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45448</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>44678</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>44908</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24954,7 +24954,7 @@
         <v>45034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>44911</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>44712</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>45834</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45734</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45734</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45734</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>45931</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>46196</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
